--- a/data/trans_bre/P1404-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1404-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,94</t>
+          <t>0,9; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,78</t>
+          <t>0,32; 7,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,85</t>
+          <t>-0,51; 7,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,57</t>
+          <t>2,81; 10,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 53,59</t>
+          <t>5,58; 53,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 39,59</t>
+          <t>1,33; 39,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 36,17</t>
+          <t>-1,9; 35,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 44,05</t>
+          <t>10,31; 50,36</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>-8,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,99</t>
+          <t>-1,26; 2,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,7</t>
+          <t>-1,97; 1,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,05</t>
+          <t>-1,34; 2,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 31,16</t>
+          <t>-2,82; 0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 44,72</t>
+          <t>-21,13; 42,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 28,92</t>
+          <t>-24,59; 27,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 28,95</t>
+          <t>-15,46; 31,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 329,53</t>
+          <t>-20,39; 6,92</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,16</t>
+          <t>-3,04; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -0,07</t>
+          <t>-7,16; -0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 1,37</t>
+          <t>-5,84; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,24</t>
+          <t>-2,78; 3,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 66,19</t>
+          <t>-49,54; 62,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,68; 3,06</t>
+          <t>-75,93; -5,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 20,46</t>
+          <t>-55,55; 20,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 34,2</t>
+          <t>-19,84; 34,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,75</t>
+          <t>1,03; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,2</t>
+          <t>1,0; 4,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,39</t>
+          <t>0,13; 3,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 25,06</t>
+          <t>0,18; 3,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 51,37</t>
+          <t>12,4; 54,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 38,63</t>
+          <t>7,79; 39,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 32,8</t>
+          <t>0,86; 31,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 190,07</t>
+          <t>1,15; 24,02</t>
         </is>
       </c>
     </row>
